--- a/hira_material_automation/output/monthly/202601_202608__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__temporary_synovial_substitute__250099__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:16:25</t>
+          <t>2026-08-14T21:28:22</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>523fdbf98fd661f4f0240c0b5e49f145d716598f0e8e9ecaab7bef0794944015</t>
+          <t>6d743db3f3f18becf6aea5f7e1d40670d53241f27a5da2952edf0e9dbd6c9b5e</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__temporary_synovial_substitute__250099__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:28:22</t>
+          <t>2026-08-24T21:33:32</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6d743db3f3f18becf6aea5f7e1d40670d53241f27a5da2952edf0e9dbd6c9b5e</t>
+          <t>3554a166c75c8c03a5b51f11dcacefa1907fe04705c26dc2af343549b6169f1a</t>
         </is>
       </c>
     </row>
